--- a/6501.T_settings.xlsx
+++ b/6501.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -478,7 +493,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -491,33 +506,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>59.25925925925925</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>76.7022594038572</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.840824422365082</v>
+      </c>
+      <c r="I2" t="n">
+        <v>767022.5940385719</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1767022.594038572</v>
+      </c>
+      <c r="K2" t="n">
+        <v>74389.01387665658</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.44444444444444</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12.30926697587815</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -529,42 +545,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>59.25925925925925</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>75.47398329877375</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.795332714769398</v>
+      </c>
+      <c r="I3" t="n">
+        <v>754739.8329877374</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1754739.832987737</v>
+      </c>
+      <c r="K3" t="n">
+        <v>74200.45219615033</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11.62962962962963</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12.30926697587814</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,11 +589,11 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,33 +602,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>59.25925925925925</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>72.17092078897784</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.672997066258438</v>
+      </c>
+      <c r="I4" t="n">
+        <v>721709.2078897783</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1721709.207889778</v>
+      </c>
+      <c r="K4" t="n">
+        <v>72507.05754098414</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12.51851851851852</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12.30926697587816</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -619,46 +637,47 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>56.03549581658049</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.807596639244532</v>
+      </c>
+      <c r="I5" t="n">
+        <v>560354.9581658049</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1560354.958165805</v>
+      </c>
+      <c r="K5" t="n">
+        <v>78374.90270885252</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13.35483870967742</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18.53790632324704</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -670,42 +689,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>55.66785322563749</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.739620413301171</v>
+      </c>
+      <c r="I6" t="n">
+        <v>556678.5322563748</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1556678.532256375</v>
+      </c>
+      <c r="K6" t="n">
+        <v>79902.98003497659</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.53125</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18.53790632324704</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,11 +733,11 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -726,33 +746,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>53.29165417041995</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.665364192825624</v>
+      </c>
+      <c r="I7" t="n">
+        <v>532916.5417041995</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1532916.5417042</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85238.82674994561</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13.46875</v>
+      </c>
+      <c r="M7" t="n">
+        <v>17.46602002806626</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,11 +781,11 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -773,33 +794,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>52.93047647418994</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.60395383255121</v>
+      </c>
+      <c r="I8" t="n">
+        <v>529304.7647418994</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1529304.764741899</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86936.05457384381</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17.46602002806624</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -807,46 +829,47 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>53.125</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>52.03538388476914</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.626105746399036</v>
+      </c>
+      <c r="I9" t="n">
+        <v>520353.8388476914</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1520353.838847691</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80099.82695003191</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.6875</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18.53790632324704</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,46 +877,47 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>51.67716614620981</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.565974731703327</v>
+      </c>
+      <c r="I10" t="n">
+        <v>516771.6614620981</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1516771.661462098</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81623.84010079714</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.87878787878788</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18.53790632324704</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -914,33 +938,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>51.05525330850843</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.760525976155463</v>
+      </c>
+      <c r="I11" t="n">
+        <v>510552.5330850843</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1510552.533085084</v>
+      </c>
+      <c r="K11" t="n">
+        <v>73805.6078625152</v>
+      </c>
+      <c r="L11" t="n">
+        <v>14.10344827586207</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17.46602002806628</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,7 +973,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -957,37 +982,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>50.69934490182661</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.68997816339422</v>
+      </c>
+      <c r="I12" t="n">
+        <v>506993.4490182661</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1506993.449018266</v>
+      </c>
+      <c r="K12" t="n">
+        <v>75412.69407626026</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17.46602002806626</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -999,42 +1025,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>44.17121826802187</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.208560913401094</v>
+      </c>
+      <c r="I13" t="n">
+        <v>441712.1826802187</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1441712.182680219</v>
+      </c>
+      <c r="K13" t="n">
+        <v>53681.13603046857</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12.42624982322318</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1046,42 +1073,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>39.30663478404875</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.403808385144598</v>
+      </c>
+      <c r="I14" t="n">
+        <v>393066.3478404875</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1393066.347840487</v>
+      </c>
+      <c r="K14" t="n">
+        <v>73955.64432267743</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17.7037021518588</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1093,7 +1121,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1102,33 +1130,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>37.21193795064048</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.488477518025619</v>
+      </c>
+      <c r="I15" t="n">
+        <v>372119.3795064047</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1372119.379506405</v>
+      </c>
+      <c r="K15" t="n">
+        <v>65223.51061303227</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.57612356634071</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>36.82678424135084</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.115963158828813</v>
+      </c>
+      <c r="I16" t="n">
+        <v>368267.8424135083</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1368267.842413508</v>
+      </c>
+      <c r="K16" t="n">
+        <v>78715.71539809486</v>
+      </c>
+      <c r="L16" t="n">
+        <v>11.51515151515152</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17.46602002806626</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1213,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1192,37 +1222,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>52.94117647058824</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3170200118882504</v>
+        <v>34.42072255040745</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-3,170円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>41日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.012374192659043</v>
+      </c>
+      <c r="I17" t="n">
+        <v>344207.2255040745</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1344207.225504074</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85751.61852448442</v>
+      </c>
+      <c r="L17" t="n">
+        <v>11.67647058823529</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20.08028573005337</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1230,46 +1261,47 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3170200118882504</v>
+        <v>34.17072278916049</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-0.32%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-3,170円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>41日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.708536139458025</v>
+      </c>
+      <c r="I18" t="n">
+        <v>341707.2278916049</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1341707.227891605</v>
+      </c>
+      <c r="K18" t="n">
+        <v>50362.25017829584</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12.42624982322315</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1281,7 +1313,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1290,33 +1322,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.497483546264034</v>
+        <v>33.31910511122155</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-5.50%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-54,975円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>11日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9799736797418102</v>
+      </c>
+      <c r="I19" t="n">
+        <v>333191.0511122155</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1333191.051112216</v>
+      </c>
+      <c r="K19" t="n">
+        <v>80449.46921756839</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11.88235294117647</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17.46602002806627</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1357,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1337,33 +1370,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.497483546264034</v>
+        <v>32.57748116069874</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-5.50%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-54,975円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>11日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.252980044642259</v>
+      </c>
+      <c r="I20" t="n">
+        <v>325774.8116069874</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1325774.811606987</v>
+      </c>
+      <c r="K20" t="n">
+        <v>66667.59165825063</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12.26923076923077</v>
+      </c>
+      <c r="M20" t="n">
+        <v>17.57612356634069</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1375,7 +1409,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1384,33 +1418,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.497483546264034</v>
+        <v>32.45950386890783</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-5.50%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-54,975円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>11日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.047080769964769</v>
+      </c>
+      <c r="I21" t="n">
+        <v>324595.0386890783</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1324595.038689078</v>
+      </c>
+      <c r="K21" t="n">
+        <v>74287.75073221041</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12.09677419354839</v>
+      </c>
+      <c r="M21" t="n">
+        <v>17.46602002806626</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.497483546264034</v>
+        <v>32.12502079900084</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-5.50%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-54,975円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>11日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.606251039950042</v>
+      </c>
+      <c r="I22" t="n">
+        <v>321250.2079900084</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1321250.207990008</v>
+      </c>
+      <c r="K22" t="n">
+        <v>49609.63885162483</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.42624982322316</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1469,42 +1505,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.643602628527251</v>
+        <v>29.38837083519145</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-5.64%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-56,436円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.099169345370818</v>
+      </c>
+      <c r="I23" t="n">
+        <v>293883.7083519145</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1293883.708351915</v>
+      </c>
+      <c r="K23" t="n">
+        <v>33907.89781028811</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12.14285714285714</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7.479544068048355</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1521,37 +1558,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.643602628527251</v>
+        <v>27.66689662054272</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-5.64%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-56,436円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9881034507336686</v>
+      </c>
+      <c r="I24" t="n">
+        <v>276668.9662054272</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1276668.966205427</v>
+      </c>
+      <c r="K24" t="n">
+        <v>68863.59248046557</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.46428571428571</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17.7037021518588</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,46 +1597,47 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.643602628527251</v>
+        <v>26.91613137749345</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-5.64%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-56,436円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.922580812678104</v>
+      </c>
+      <c r="I25" t="n">
+        <v>269161.3137749345</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1269161.313774935</v>
+      </c>
+      <c r="K25" t="n">
+        <v>33390.42640636054</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12.35714285714286</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.479544068048345</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1610,42 +1649,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.394502516453735</v>
+        <v>26.91613137749345</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-7.39%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-73,945円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.922580812678104</v>
+      </c>
+      <c r="I26" t="n">
+        <v>269161.3137749345</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1269161.313774935</v>
+      </c>
+      <c r="K26" t="n">
+        <v>33390.42640636054</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.35714285714286</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7.479544068048345</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1657,42 +1697,43 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.394502516453735</v>
+        <v>25.74722176444796</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-7.39%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-73,945円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.029888870577918</v>
+      </c>
+      <c r="I27" t="n">
+        <v>257472.2176444796</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1257472.21764448</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60873.13210478905</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17.57612356634069</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1713,33 +1754,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="F28" t="n">
-        <v>-7.394502516453735</v>
+        <v>21.49999608987</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-7.39%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-73,945円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8269229265334613</v>
+      </c>
+      <c r="I28" t="n">
+        <v>214999.9608986999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1214999.9608987</v>
+      </c>
+      <c r="K28" t="n">
+        <v>62196.55324547894</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.15384615384615</v>
+      </c>
+      <c r="M28" t="n">
+        <v>17.57612356634071</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,46 +1789,47 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.394502516453735</v>
+        <v>18.80201371381602</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-7.39%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-73,945円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6715004897791435</v>
+      </c>
+      <c r="I29" t="n">
+        <v>188020.1371381602</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1188020.13713816</v>
+      </c>
+      <c r="K29" t="n">
+        <v>67093.79179439023</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10.35714285714286</v>
+      </c>
+      <c r="M29" t="n">
+        <v>17.70370215185881</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,11 +1837,11 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1807,33 +1850,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.537688442211055</v>
+        <v>18.70650086468747</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-7.54%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-75,377円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.7482600345874988</v>
+      </c>
+      <c r="I30" t="n">
+        <v>187065.0086468747</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1187065.008646875</v>
+      </c>
+      <c r="K30" t="n">
+        <v>59489.96497587956</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="M30" t="n">
+        <v>17.57612356634069</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1841,11 +1885,11 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1854,33 +1898,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="F31" t="n">
-        <v>-7.537688442211055</v>
+        <v>17.24554700686818</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-7.54%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-75,377円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6387239632173398</v>
+      </c>
+      <c r="I31" t="n">
+        <v>172455.4700686818</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1172455.470068682</v>
+      </c>
+      <c r="K31" t="n">
+        <v>62424.99571091936</v>
+      </c>
+      <c r="L31" t="n">
+        <v>12.62962962962963</v>
+      </c>
+      <c r="M31" t="n">
+        <v>17.96011141469991</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1888,46 +1933,47 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="F32" t="n">
-        <v>-7.537688442211055</v>
+        <v>14.69719392880662</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-7.54%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-75,377円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5652766895694855</v>
+      </c>
+      <c r="I32" t="n">
+        <v>146971.9392880662</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1146971.939288066</v>
+      </c>
+      <c r="K32" t="n">
+        <v>60909.34017978676</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.23076923076923</v>
+      </c>
+      <c r="M32" t="n">
+        <v>17.57612356634069</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,46 +1981,47 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F33" t="n">
-        <v>-9.481216457960643</v>
+        <v>11.98449103386842</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-9.48%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-94,812円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>17日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.443870038291423</v>
+      </c>
+      <c r="I33" t="n">
+        <v>119844.9103386842</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1119844.910338684</v>
+      </c>
+      <c r="K33" t="n">
+        <v>60737.13830267843</v>
+      </c>
+      <c r="L33" t="n">
+        <v>11.51851851851852</v>
+      </c>
+      <c r="M33" t="n">
+        <v>17.96011141469988</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,11 +2029,11 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1995,33 +2042,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="F34" t="n">
-        <v>-9.481216457960643</v>
+        <v>11.40722302509777</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-9.48%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-94,812円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>17日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.600380159215672</v>
+      </c>
+      <c r="I34" t="n">
+        <v>114072.2302509777</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1114072.230250978</v>
+      </c>
+      <c r="K34" t="n">
+        <v>41874.95039250578</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12.31578947368421</v>
+      </c>
+      <c r="M34" t="n">
+        <v>12.57659640184843</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2029,11 +2077,11 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2042,33 +2090,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="F35" t="n">
-        <v>-9.481216457960643</v>
+        <v>9.278551562141976</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-9.48%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-94,812円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>17日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.488344819060104</v>
+      </c>
+      <c r="I35" t="n">
+        <v>92785.51562141976</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1092785.51562142</v>
+      </c>
+      <c r="K35" t="n">
+        <v>41257.34378115419</v>
+      </c>
+      <c r="L35" t="n">
+        <v>12.47368421052632</v>
+      </c>
+      <c r="M35" t="n">
+        <v>13.46028191009443</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2080,7 +2129,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2089,33 +2138,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.481216457960643</v>
+        <v>9.278551562141976</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-9.48%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-94,812円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>17日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.488344819060104</v>
+      </c>
+      <c r="I36" t="n">
+        <v>92785.51562141976</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1092785.51562142</v>
+      </c>
+      <c r="K36" t="n">
+        <v>41257.34378115419</v>
+      </c>
+      <c r="L36" t="n">
+        <v>12.47368421052632</v>
+      </c>
+      <c r="M36" t="n">
+        <v>13.46028191009443</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,46 +2173,47 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.89159891598916</v>
+        <v>4.208556734037632</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-98,916円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1558724716310234</v>
+      </c>
+      <c r="I37" t="n">
+        <v>42085.56734037632</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1042085.567340376</v>
+      </c>
+      <c r="K37" t="n">
+        <v>59369.5153729961</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.40740740740741</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22.00225662859165</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,46 +2221,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-9.89159891598916</v>
+        <v>1.155974045872327</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-98,916円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07224837786702046</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11559.74045872327</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1011559.740458723</v>
+      </c>
+      <c r="K38" t="n">
+        <v>33752.68722282434</v>
+      </c>
+      <c r="L38" t="n">
+        <v>10.6875</v>
+      </c>
+      <c r="M38" t="n">
+        <v>15.29501113708905</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2217,7 +2269,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2226,37 +2278,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-9.89159891598916</v>
+        <v>1.155974045872327</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-98,916円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07224837786702046</v>
+      </c>
+      <c r="I39" t="n">
+        <v>11559.74045872327</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1011559.740458723</v>
+      </c>
+      <c r="K39" t="n">
+        <v>33752.68722282434</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10.6875</v>
+      </c>
+      <c r="M39" t="n">
+        <v>15.29501113708905</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,46 +2317,47 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-9.89159891598916</v>
+        <v>-0.6758858331098337</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-9.89%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-98,916円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.04224286456936461</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-6758.858331098338</v>
+      </c>
+      <c r="J40" t="n">
+        <v>993241.1416689017</v>
+      </c>
+      <c r="K40" t="n">
+        <v>33507.91842177721</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12.125</v>
+      </c>
+      <c r="M40" t="n">
+        <v>16.50163698653884</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2311,46 +2365,47 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-10.03092385001933</v>
+        <v>-0.6758858331098337</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-10.03%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-100,309円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.04224286456936461</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-6758.858331098338</v>
+      </c>
+      <c r="J41" t="n">
+        <v>993241.1416689017</v>
+      </c>
+      <c r="K41" t="n">
+        <v>33507.91842177721</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12.125</v>
+      </c>
+      <c r="M41" t="n">
+        <v>16.50163698653884</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2362,42 +2417,43 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-10.03092385001933</v>
+        <v>-3.810681878897885</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-10.03%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-100,309円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.2381676174311178</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-38106.81878897885</v>
+      </c>
+      <c r="J42" t="n">
+        <v>961893.1812110211</v>
+      </c>
+      <c r="K42" t="n">
+        <v>32548.91122593718</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.4375</v>
+      </c>
+      <c r="M42" t="n">
+        <v>16.50163698653883</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2409,7 +2465,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,33 +2474,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-10.03092385001933</v>
+        <v>-3.810681878897885</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-10.03%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-100,309円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.2381676174311178</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-38106.81878897885</v>
+      </c>
+      <c r="J43" t="n">
+        <v>961893.1812110211</v>
+      </c>
+      <c r="K43" t="n">
+        <v>32548.91122593718</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.4375</v>
+      </c>
+      <c r="M43" t="n">
+        <v>16.50163698653883</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,11 +2509,11 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2465,33 +2522,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>-10.99185052673425</v>
+        <v>-6.732946717138379</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-10.99%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-109,919円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>18日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.3740525953965766</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-67329.46717138379</v>
+      </c>
+      <c r="J44" t="n">
+        <v>932670.5328286162</v>
+      </c>
+      <c r="K44" t="n">
+        <v>36347.00774821512</v>
+      </c>
+      <c r="L44" t="n">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="M44" t="n">
+        <v>18.69846659257183</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2503,7 +2561,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2512,33 +2570,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F45" t="n">
-        <v>-10.99185052673425</v>
+        <v>-8.51501173380675</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-10.99%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-109,919円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>18日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.4730562074337084</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-85150.1173380675</v>
+      </c>
+      <c r="J45" t="n">
+        <v>914849.8826619325</v>
+      </c>
+      <c r="K45" t="n">
+        <v>35809.47426507939</v>
+      </c>
+      <c r="L45" t="n">
+        <v>11.27777777777778</v>
+      </c>
+      <c r="M45" t="n">
+        <v>19.01717373619948</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2546,7 +2605,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2559,33 +2618,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F46" t="n">
-        <v>-13.09357290790114</v>
+        <v>-8.51501173380675</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-6.55%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-130,936円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>14日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>5.64%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.4730562074337084</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-85150.1173380675</v>
+      </c>
+      <c r="J46" t="n">
+        <v>914849.8826619325</v>
+      </c>
+      <c r="K46" t="n">
+        <v>35809.47426507939</v>
+      </c>
+      <c r="L46" t="n">
+        <v>11.27777777777778</v>
+      </c>
+      <c r="M46" t="n">
+        <v>19.01717373619948</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/6501.T_settings.xlsx
+++ b/6501.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>59.25925925925925</v>
       </c>
       <c r="F2" t="n">
-        <v>76.7022594038572</v>
+        <v>76.70220168158933</v>
       </c>
       <c r="G2" t="n">
         <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>2.840824422365082</v>
+        <v>2.840822284503309</v>
       </c>
       <c r="I2" t="n">
-        <v>767022.5940385719</v>
+        <v>767022.0168158934</v>
       </c>
       <c r="J2" t="n">
-        <v>1767022.594038572</v>
+        <v>1767022.016815893</v>
       </c>
       <c r="K2" t="n">
-        <v>74389.01387665658</v>
+        <v>74389.00217521904</v>
       </c>
       <c r="L2" t="n">
         <v>12.44444444444444</v>
       </c>
       <c r="M2" t="n">
-        <v>12.30926697587815</v>
+        <v>12.30926697587814</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,22 +557,22 @@
         <v>59.25925925925925</v>
       </c>
       <c r="F3" t="n">
-        <v>75.47398329877375</v>
+        <v>75.4739698290205</v>
       </c>
       <c r="G3" t="n">
         <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>2.795332714769398</v>
+        <v>2.795332215889648</v>
       </c>
       <c r="I3" t="n">
-        <v>754739.8329877374</v>
+        <v>754739.6982902051</v>
       </c>
       <c r="J3" t="n">
-        <v>1754739.832987737</v>
+        <v>1754739.698290205</v>
       </c>
       <c r="K3" t="n">
-        <v>74200.45219615033</v>
+        <v>74200.45743117222</v>
       </c>
       <c r="L3" t="n">
         <v>11.62962962962963</v>
@@ -605,28 +605,28 @@
         <v>59.25925925925925</v>
       </c>
       <c r="F4" t="n">
-        <v>72.17092078897784</v>
+        <v>72.17081348023061</v>
       </c>
       <c r="G4" t="n">
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>2.672997066258438</v>
+        <v>2.672993091860393</v>
       </c>
       <c r="I4" t="n">
-        <v>721709.2078897783</v>
+        <v>721708.1348023061</v>
       </c>
       <c r="J4" t="n">
-        <v>1721709.207889778</v>
+        <v>1721708.134802306</v>
       </c>
       <c r="K4" t="n">
-        <v>72507.05754098414</v>
+        <v>72507.02493058123</v>
       </c>
       <c r="L4" t="n">
         <v>12.51851851851852</v>
       </c>
       <c r="M4" t="n">
-        <v>12.30926697587816</v>
+        <v>12.30926697587814</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>54.83870967741935</v>
       </c>
       <c r="F5" t="n">
-        <v>56.03549581658049</v>
+        <v>56.03544661302134</v>
       </c>
       <c r="G5" t="n">
         <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>1.807596639244532</v>
+        <v>1.807595052032946</v>
       </c>
       <c r="I5" t="n">
-        <v>560354.9581658049</v>
+        <v>560354.4661302133</v>
       </c>
       <c r="J5" t="n">
-        <v>1560354.958165805</v>
+        <v>1560354.466130213</v>
       </c>
       <c r="K5" t="n">
-        <v>78374.90270885252</v>
+        <v>78374.89049075799</v>
       </c>
       <c r="L5" t="n">
         <v>13.35483870967742</v>
       </c>
       <c r="M5" t="n">
-        <v>18.53790632324704</v>
+        <v>18.5378982279476</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>56.25</v>
       </c>
       <c r="F6" t="n">
-        <v>55.66785322563749</v>
+        <v>55.66778770249633</v>
       </c>
       <c r="G6" t="n">
         <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>1.739620413301171</v>
+        <v>1.73961836570301</v>
       </c>
       <c r="I6" t="n">
-        <v>556678.5322563748</v>
+        <v>556677.8770249633</v>
       </c>
       <c r="J6" t="n">
-        <v>1556678.532256375</v>
+        <v>1556677.877024963</v>
       </c>
       <c r="K6" t="n">
-        <v>79902.98003497659</v>
+        <v>79902.96081102428</v>
       </c>
       <c r="L6" t="n">
         <v>12.53125</v>
       </c>
       <c r="M6" t="n">
-        <v>18.53790632324704</v>
+        <v>18.5378982279476</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>56.25</v>
       </c>
       <c r="F7" t="n">
-        <v>53.29165417041995</v>
+        <v>53.29156621985533</v>
       </c>
       <c r="G7" t="n">
         <v>32</v>
       </c>
       <c r="H7" t="n">
-        <v>1.665364192825624</v>
+        <v>1.665361444370479</v>
       </c>
       <c r="I7" t="n">
-        <v>532916.5417041995</v>
+        <v>532915.6621985533</v>
       </c>
       <c r="J7" t="n">
-        <v>1532916.5417042</v>
+        <v>1532915.662198553</v>
       </c>
       <c r="K7" t="n">
-        <v>85238.82674994561</v>
+        <v>85238.79479441275</v>
       </c>
       <c r="L7" t="n">
         <v>13.46875</v>
       </c>
       <c r="M7" t="n">
-        <v>17.46602002806626</v>
+        <v>17.46602002806627</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>57.57575757575758</v>
       </c>
       <c r="F8" t="n">
-        <v>52.93047647418994</v>
+        <v>52.93037258435492</v>
       </c>
       <c r="G8" t="n">
         <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>1.60395383255121</v>
+        <v>1.603950684374392</v>
       </c>
       <c r="I8" t="n">
-        <v>529304.7647418994</v>
+        <v>529303.7258435492</v>
       </c>
       <c r="J8" t="n">
-        <v>1529304.764741899</v>
+        <v>1529303.725843549</v>
       </c>
       <c r="K8" t="n">
-        <v>86936.05457384381</v>
+        <v>86936.01467052662</v>
       </c>
       <c r="L8" t="n">
         <v>12.66666666666667</v>
       </c>
       <c r="M8" t="n">
-        <v>17.46602002806624</v>
+        <v>17.46602002806627</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>53.125</v>
       </c>
       <c r="F9" t="n">
-        <v>52.03538388476914</v>
+        <v>52.0353266463253</v>
       </c>
       <c r="G9" t="n">
         <v>32</v>
       </c>
       <c r="H9" t="n">
-        <v>1.626105746399036</v>
+        <v>1.626103957697665</v>
       </c>
       <c r="I9" t="n">
-        <v>520353.8388476914</v>
+        <v>520353.2664632529</v>
       </c>
       <c r="J9" t="n">
-        <v>1520353.838847691</v>
+        <v>1520353.266463253</v>
       </c>
       <c r="K9" t="n">
-        <v>80099.82695003191</v>
+        <v>80099.81221778989</v>
       </c>
       <c r="L9" t="n">
         <v>13.6875</v>
       </c>
       <c r="M9" t="n">
-        <v>18.53790632324704</v>
+        <v>18.5378982279476</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>54.54545454545454</v>
       </c>
       <c r="F10" t="n">
-        <v>51.67716614620981</v>
+        <v>51.67709302845558</v>
       </c>
       <c r="G10" t="n">
         <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>1.565974731703327</v>
+        <v>1.565972516013805</v>
       </c>
       <c r="I10" t="n">
-        <v>516771.6614620981</v>
+        <v>516770.9302845558</v>
       </c>
       <c r="J10" t="n">
-        <v>1516771.661462098</v>
+        <v>1516770.930284556</v>
       </c>
       <c r="K10" t="n">
-        <v>81623.84010079714</v>
+        <v>81623.81818693172</v>
       </c>
       <c r="L10" t="n">
         <v>12.87878787878788</v>
       </c>
       <c r="M10" t="n">
-        <v>18.53790632324704</v>
+        <v>18.5378982279476</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>55.17241379310344</v>
       </c>
       <c r="F11" t="n">
-        <v>51.05525330850843</v>
+        <v>51.05522378448991</v>
       </c>
       <c r="G11" t="n">
         <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>1.760525976155463</v>
+        <v>1.760524958085859</v>
       </c>
       <c r="I11" t="n">
-        <v>510552.5330850843</v>
+        <v>510552.2378448991</v>
       </c>
       <c r="J11" t="n">
-        <v>1510552.533085084</v>
+        <v>1510552.237844899</v>
       </c>
       <c r="K11" t="n">
-        <v>73805.6078625152</v>
+        <v>73805.60316029635</v>
       </c>
       <c r="L11" t="n">
         <v>14.10344827586207</v>
       </c>
       <c r="M11" t="n">
-        <v>17.46602002806628</v>
+        <v>17.46602002806626</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>56.66666666666666</v>
       </c>
       <c r="F12" t="n">
-        <v>50.69934490182661</v>
+        <v>50.69929953643445</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
       </c>
       <c r="H12" t="n">
-        <v>1.68997816339422</v>
+        <v>1.689976651214482</v>
       </c>
       <c r="I12" t="n">
-        <v>506993.4490182661</v>
+        <v>506992.9953643444</v>
       </c>
       <c r="J12" t="n">
-        <v>1506993.449018266</v>
+        <v>1506992.995364344</v>
       </c>
       <c r="K12" t="n">
-        <v>75412.69407626026</v>
+        <v>75412.68267467769</v>
       </c>
       <c r="L12" t="n">
         <v>13.2</v>
       </c>
       <c r="M12" t="n">
-        <v>17.46602002806626</v>
+        <v>17.46602002806628</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>55.00000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>44.17121826802187</v>
+        <v>44.17114794776884</v>
       </c>
       <c r="G13" t="n">
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>2.208560913401094</v>
+        <v>2.208557397388442</v>
       </c>
       <c r="I13" t="n">
-        <v>441712.1826802187</v>
+        <v>441711.4794776884</v>
       </c>
       <c r="J13" t="n">
-        <v>1441712.182680219</v>
+        <v>1441711.479477688</v>
       </c>
       <c r="K13" t="n">
-        <v>53681.13603046857</v>
+        <v>53681.11418864402</v>
       </c>
       <c r="L13" t="n">
         <v>10.3</v>
       </c>
       <c r="M13" t="n">
-        <v>12.42624982322318</v>
+        <v>12.42624982322317</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>39.30663478404875</v>
+        <v>39.30649318167663</v>
       </c>
       <c r="G14" t="n">
         <v>28</v>
       </c>
       <c r="H14" t="n">
-        <v>1.403808385144598</v>
+        <v>1.403803327917023</v>
       </c>
       <c r="I14" t="n">
-        <v>393066.3478404875</v>
+        <v>393064.9318167663</v>
       </c>
       <c r="J14" t="n">
-        <v>1393066.347840487</v>
+        <v>1393064.931816766</v>
       </c>
       <c r="K14" t="n">
-        <v>73955.64432267743</v>
+        <v>73955.58047276572</v>
       </c>
       <c r="L14" t="n">
         <v>11.5</v>
       </c>
       <c r="M14" t="n">
-        <v>17.7037021518588</v>
+        <v>17.70370215185882</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>37.21193795064048</v>
+        <v>37.21185401003495</v>
       </c>
       <c r="G15" t="n">
         <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>1.488477518025619</v>
+        <v>1.488474160401398</v>
       </c>
       <c r="I15" t="n">
-        <v>372119.3795064047</v>
+        <v>372118.5401003496</v>
       </c>
       <c r="J15" t="n">
-        <v>1372119.379506405</v>
+        <v>1372118.54010035</v>
       </c>
       <c r="K15" t="n">
-        <v>65223.51061303227</v>
+        <v>65223.47763364946</v>
       </c>
       <c r="L15" t="n">
         <v>13.36</v>
       </c>
       <c r="M15" t="n">
-        <v>17.57612356634071</v>
+        <v>17.57612356634068</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>51.51515151515152</v>
       </c>
       <c r="F16" t="n">
-        <v>36.82678424135084</v>
+        <v>36.82676084199269</v>
       </c>
       <c r="G16" t="n">
         <v>33</v>
       </c>
       <c r="H16" t="n">
-        <v>1.115963158828813</v>
+        <v>1.115962449757354</v>
       </c>
       <c r="I16" t="n">
-        <v>368267.8424135083</v>
+        <v>368267.6084199268</v>
       </c>
       <c r="J16" t="n">
-        <v>1368267.842413508</v>
+        <v>1368267.608419927</v>
       </c>
       <c r="K16" t="n">
-        <v>78715.71539809486</v>
+        <v>78715.71337240003</v>
       </c>
       <c r="L16" t="n">
         <v>11.51515151515152</v>
       </c>
       <c r="M16" t="n">
-        <v>17.46602002806626</v>
+        <v>17.46602002806629</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>52.94117647058824</v>
       </c>
       <c r="F17" t="n">
-        <v>34.42072255040745</v>
+        <v>34.42066482673374</v>
       </c>
       <c r="G17" t="n">
         <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>1.012374192659043</v>
+        <v>1.012372494903934</v>
       </c>
       <c r="I17" t="n">
-        <v>344207.2255040745</v>
+        <v>344206.6482673374</v>
       </c>
       <c r="J17" t="n">
-        <v>1344207.225504074</v>
+        <v>1344206.648267337</v>
       </c>
       <c r="K17" t="n">
-        <v>85751.61852448442</v>
+        <v>85751.5976327627</v>
       </c>
       <c r="L17" t="n">
         <v>11.67647058823529</v>
       </c>
       <c r="M17" t="n">
-        <v>20.08028573005337</v>
+        <v>20.08029605363438</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>34.17072278916049</v>
+        <v>34.17068381611421</v>
       </c>
       <c r="G18" t="n">
         <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>1.708536139458025</v>
+        <v>1.70853419080571</v>
       </c>
       <c r="I18" t="n">
-        <v>341707.2278916049</v>
+        <v>341706.8381611421</v>
       </c>
       <c r="J18" t="n">
-        <v>1341707.227891605</v>
+        <v>1341706.838161142</v>
       </c>
       <c r="K18" t="n">
-        <v>50362.25017829584</v>
+        <v>50362.23950965431</v>
       </c>
       <c r="L18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>12.42624982322315</v>
+        <v>12.42624982322318</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>33.31910511122155</v>
+        <v>33.31907415987756</v>
       </c>
       <c r="G19" t="n">
         <v>34</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9799736797418102</v>
+        <v>0.9799727694081635</v>
       </c>
       <c r="I19" t="n">
-        <v>333191.0511122155</v>
+        <v>333190.7415987756</v>
       </c>
       <c r="J19" t="n">
-        <v>1333191.051112216</v>
+        <v>1333190.741598776</v>
       </c>
       <c r="K19" t="n">
-        <v>80449.46921756839</v>
+        <v>80449.46500122854</v>
       </c>
       <c r="L19" t="n">
         <v>11.88235294117647</v>
       </c>
       <c r="M19" t="n">
-        <v>17.46602002806627</v>
+        <v>17.46602002806626</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>32.57748116069874</v>
+        <v>32.57739334290782</v>
       </c>
       <c r="G20" t="n">
         <v>26</v>
       </c>
       <c r="H20" t="n">
-        <v>1.252980044642259</v>
+        <v>1.252976667034916</v>
       </c>
       <c r="I20" t="n">
-        <v>325774.8116069874</v>
+        <v>325773.9334290782</v>
       </c>
       <c r="J20" t="n">
-        <v>1325774.811606987</v>
+        <v>1325773.933429078</v>
       </c>
       <c r="K20" t="n">
-        <v>66667.59165825063</v>
+        <v>66667.5548591096</v>
       </c>
       <c r="L20" t="n">
         <v>12.26923076923077</v>
       </c>
       <c r="M20" t="n">
-        <v>17.57612356634069</v>
+        <v>17.57612356634071</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>51.61290322580645</v>
       </c>
       <c r="F21" t="n">
-        <v>32.45950386890783</v>
+        <v>32.45949709618152</v>
       </c>
       <c r="G21" t="n">
         <v>31</v>
       </c>
       <c r="H21" t="n">
-        <v>1.047080769964769</v>
+        <v>1.047080551489727</v>
       </c>
       <c r="I21" t="n">
-        <v>324595.0386890783</v>
+        <v>324594.9709618152</v>
       </c>
       <c r="J21" t="n">
-        <v>1324595.038689078</v>
+        <v>1324594.970961815</v>
       </c>
       <c r="K21" t="n">
-        <v>74287.75073221041</v>
+        <v>74287.75562599245</v>
       </c>
       <c r="L21" t="n">
         <v>12.09677419354839</v>
       </c>
       <c r="M21" t="n">
-        <v>17.46602002806626</v>
+        <v>17.46602002806628</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>32.12502079900084</v>
+        <v>32.12495712511495</v>
       </c>
       <c r="G22" t="n">
         <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>1.606251039950042</v>
+        <v>1.606247856255748</v>
       </c>
       <c r="I22" t="n">
-        <v>321250.2079900084</v>
+        <v>321249.5712511495</v>
       </c>
       <c r="J22" t="n">
-        <v>1321250.207990008</v>
+        <v>1321249.57125115</v>
       </c>
       <c r="K22" t="n">
-        <v>49609.63885162483</v>
+        <v>49609.61903962429</v>
       </c>
       <c r="L22" t="n">
         <v>8.85</v>
       </c>
       <c r="M22" t="n">
-        <v>12.42624982322316</v>
+        <v>12.42624982322318</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>29.38837083519145</v>
+        <v>29.38833292899772</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>2.099169345370818</v>
+        <v>2.099166637785551</v>
       </c>
       <c r="I23" t="n">
-        <v>293883.7083519145</v>
+        <v>293883.3292899772</v>
       </c>
       <c r="J23" t="n">
-        <v>1293883.708351915</v>
+        <v>1293883.329289977</v>
       </c>
       <c r="K23" t="n">
-        <v>33907.89781028811</v>
+        <v>33907.89072123803</v>
       </c>
       <c r="L23" t="n">
         <v>12.14285714285714</v>
       </c>
       <c r="M23" t="n">
-        <v>7.479544068048355</v>
+        <v>7.479544068048352</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>46.42857142857143</v>
       </c>
       <c r="F24" t="n">
-        <v>27.66689662054272</v>
+        <v>27.66676759449353</v>
       </c>
       <c r="G24" t="n">
         <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9881034507336686</v>
+        <v>0.9880988426604832</v>
       </c>
       <c r="I24" t="n">
-        <v>276668.9662054272</v>
+        <v>276667.6759449353</v>
       </c>
       <c r="J24" t="n">
-        <v>1276668.966205427</v>
+        <v>1276667.675944935</v>
       </c>
       <c r="K24" t="n">
-        <v>68863.59248046557</v>
+        <v>68863.53379178869</v>
       </c>
       <c r="L24" t="n">
         <v>10.46428571428571</v>
       </c>
       <c r="M24" t="n">
-        <v>17.7037021518588</v>
+        <v>17.70370215185881</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,22 +1613,22 @@
         <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>26.91613137749345</v>
+        <v>26.91606989822248</v>
       </c>
       <c r="G25" t="n">
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>1.922580812678104</v>
+        <v>1.922576421301606</v>
       </c>
       <c r="I25" t="n">
-        <v>269161.3137749345</v>
+        <v>269160.6989822248</v>
       </c>
       <c r="J25" t="n">
-        <v>1269161.313774935</v>
+        <v>1269160.698982225</v>
       </c>
       <c r="K25" t="n">
-        <v>33390.42640636054</v>
+        <v>33390.41322924121</v>
       </c>
       <c r="L25" t="n">
         <v>12.35714285714286</v>
@@ -1661,22 +1661,22 @@
         <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>26.91613137749345</v>
+        <v>26.91606989822248</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>1.922580812678104</v>
+        <v>1.922576421301606</v>
       </c>
       <c r="I26" t="n">
-        <v>269161.3137749345</v>
+        <v>269160.6989822248</v>
       </c>
       <c r="J26" t="n">
-        <v>1269161.313774935</v>
+        <v>1269160.698982225</v>
       </c>
       <c r="K26" t="n">
-        <v>33390.42640636054</v>
+        <v>33390.41322924121</v>
       </c>
       <c r="L26" t="n">
         <v>12.35714285714286</v>
@@ -1709,28 +1709,28 @@
         <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>25.74722176444796</v>
+        <v>25.74714557104956</v>
       </c>
       <c r="G27" t="n">
         <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>1.029888870577918</v>
+        <v>1.029885822841982</v>
       </c>
       <c r="I27" t="n">
-        <v>257472.2176444796</v>
+        <v>257471.4557104956</v>
       </c>
       <c r="J27" t="n">
-        <v>1257472.21764448</v>
+        <v>1257471.455710496</v>
       </c>
       <c r="K27" t="n">
-        <v>60873.13210478905</v>
+        <v>60873.10189340232</v>
       </c>
       <c r="L27" t="n">
         <v>12.2</v>
       </c>
       <c r="M27" t="n">
-        <v>17.57612356634069</v>
+        <v>17.5761235663407</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>46.15384615384615</v>
       </c>
       <c r="F28" t="n">
-        <v>21.49999608987</v>
+        <v>21.49991631846679</v>
       </c>
       <c r="G28" t="n">
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8269229265334613</v>
+        <v>0.826919858402569</v>
       </c>
       <c r="I28" t="n">
-        <v>214999.9608986999</v>
+        <v>214999.1631846679</v>
       </c>
       <c r="J28" t="n">
-        <v>1214999.9608987</v>
+        <v>1214999.163184668</v>
       </c>
       <c r="K28" t="n">
-        <v>62196.55324547894</v>
+        <v>62196.51954121351</v>
       </c>
       <c r="L28" t="n">
         <v>11.15384615384615</v>
       </c>
       <c r="M28" t="n">
-        <v>17.57612356634071</v>
+        <v>17.57612356634069</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F29" t="n">
-        <v>18.80201371381602</v>
+        <v>18.80191639141382</v>
       </c>
       <c r="G29" t="n">
         <v>28</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6715004897791435</v>
+        <v>0.6714970139790651</v>
       </c>
       <c r="I29" t="n">
-        <v>188020.1371381602</v>
+        <v>188019.1639141382</v>
       </c>
       <c r="J29" t="n">
-        <v>1188020.13713816</v>
+        <v>1188019.163914138</v>
       </c>
       <c r="K29" t="n">
-        <v>67093.79179439023</v>
+        <v>67093.74685900309</v>
       </c>
       <c r="L29" t="n">
         <v>10.35714285714286</v>
       </c>
       <c r="M29" t="n">
-        <v>17.70370215185881</v>
+        <v>17.70370215185879</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>44</v>
       </c>
       <c r="F30" t="n">
-        <v>18.70650086468747</v>
+        <v>18.70643627598263</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7482600345874988</v>
+        <v>0.748257451039305</v>
       </c>
       <c r="I30" t="n">
-        <v>187065.0086468747</v>
+        <v>187064.3627598262</v>
       </c>
       <c r="J30" t="n">
-        <v>1187065.008646875</v>
+        <v>1187064.362759826</v>
       </c>
       <c r="K30" t="n">
-        <v>59489.96497587956</v>
+        <v>59489.9418287455</v>
       </c>
       <c r="L30" t="n">
         <v>11.24</v>
       </c>
       <c r="M30" t="n">
-        <v>17.57612356634069</v>
+        <v>17.5761235663407</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>48.14814814814815</v>
       </c>
       <c r="F31" t="n">
-        <v>17.24554700686818</v>
+        <v>17.24545451973276</v>
       </c>
       <c r="G31" t="n">
         <v>27</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6387239632173398</v>
+        <v>0.6387205377678801</v>
       </c>
       <c r="I31" t="n">
-        <v>172455.4700686818</v>
+        <v>172454.5451973276</v>
       </c>
       <c r="J31" t="n">
-        <v>1172455.470068682</v>
+        <v>1172454.545197328</v>
       </c>
       <c r="K31" t="n">
-        <v>62424.99571091936</v>
+        <v>62424.95985288447</v>
       </c>
       <c r="L31" t="n">
         <v>12.62962962962963</v>
       </c>
       <c r="M31" t="n">
-        <v>17.96011141469991</v>
+        <v>17.96012172529384</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>42.30769230769231</v>
       </c>
       <c r="F32" t="n">
-        <v>14.69719392880662</v>
+        <v>14.69712571450032</v>
       </c>
       <c r="G32" t="n">
         <v>26</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5652766895694855</v>
+        <v>0.5652740659423199</v>
       </c>
       <c r="I32" t="n">
-        <v>146971.9392880662</v>
+        <v>146971.2571450032</v>
       </c>
       <c r="J32" t="n">
-        <v>1146971.939288066</v>
+        <v>1146971.257145003</v>
       </c>
       <c r="K32" t="n">
-        <v>60909.34017978676</v>
+        <v>60909.31396819968</v>
       </c>
       <c r="L32" t="n">
         <v>10.23076923076923</v>
       </c>
       <c r="M32" t="n">
-        <v>17.57612356634069</v>
+        <v>17.57612356634071</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>44.44444444444444</v>
       </c>
       <c r="F33" t="n">
-        <v>11.98449103386842</v>
+        <v>11.98440379419436</v>
       </c>
       <c r="G33" t="n">
         <v>27</v>
       </c>
       <c r="H33" t="n">
-        <v>0.443870038291423</v>
+        <v>0.4438668071923838</v>
       </c>
       <c r="I33" t="n">
-        <v>119844.9103386842</v>
+        <v>119844.0379419436</v>
       </c>
       <c r="J33" t="n">
-        <v>1119844.910338684</v>
+        <v>1119844.037941944</v>
       </c>
       <c r="K33" t="n">
-        <v>60737.13830267843</v>
+        <v>60737.10432626086</v>
       </c>
       <c r="L33" t="n">
         <v>11.51851851851852</v>
       </c>
       <c r="M33" t="n">
-        <v>17.96011141469988</v>
+        <v>17.96012172529382</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,22 +2045,22 @@
         <v>42.10526315789473</v>
       </c>
       <c r="F34" t="n">
-        <v>11.40722302509777</v>
+        <v>11.40711184711175</v>
       </c>
       <c r="G34" t="n">
         <v>19</v>
       </c>
       <c r="H34" t="n">
-        <v>0.600380159215672</v>
+        <v>0.6003743077427235</v>
       </c>
       <c r="I34" t="n">
-        <v>114072.2302509777</v>
+        <v>114071.1184711175</v>
       </c>
       <c r="J34" t="n">
-        <v>1114072.230250978</v>
+        <v>1114071.118471117</v>
       </c>
       <c r="K34" t="n">
-        <v>41874.95039250578</v>
+        <v>41874.9173590202</v>
       </c>
       <c r="L34" t="n">
         <v>12.31578947368421</v>
@@ -2093,28 +2093,28 @@
         <v>42.10526315789473</v>
       </c>
       <c r="F35" t="n">
-        <v>9.278551562141976</v>
+        <v>9.27842158771872</v>
       </c>
       <c r="G35" t="n">
         <v>19</v>
       </c>
       <c r="H35" t="n">
-        <v>0.488344819060104</v>
+        <v>0.4883379783009852</v>
       </c>
       <c r="I35" t="n">
-        <v>92785.51562141976</v>
+        <v>92784.21587718721</v>
       </c>
       <c r="J35" t="n">
-        <v>1092785.51562142</v>
+        <v>1092784.215877187</v>
       </c>
       <c r="K35" t="n">
-        <v>41257.34378115419</v>
+        <v>41257.30392227586</v>
       </c>
       <c r="L35" t="n">
         <v>12.47368421052632</v>
       </c>
       <c r="M35" t="n">
-        <v>13.46028191009443</v>
+        <v>13.46032304885737</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>42.10526315789473</v>
       </c>
       <c r="F36" t="n">
-        <v>9.278551562141976</v>
+        <v>9.27842158771872</v>
       </c>
       <c r="G36" t="n">
         <v>19</v>
       </c>
       <c r="H36" t="n">
-        <v>0.488344819060104</v>
+        <v>0.4883379783009852</v>
       </c>
       <c r="I36" t="n">
-        <v>92785.51562141976</v>
+        <v>92784.21587718721</v>
       </c>
       <c r="J36" t="n">
-        <v>1092785.51562142</v>
+        <v>1092784.215877187</v>
       </c>
       <c r="K36" t="n">
-        <v>41257.34378115419</v>
+        <v>41257.30392227586</v>
       </c>
       <c r="L36" t="n">
         <v>12.47368421052632</v>
       </c>
       <c r="M36" t="n">
-        <v>13.46028191009443</v>
+        <v>13.46032304885737</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>40.74074074074074</v>
       </c>
       <c r="F37" t="n">
-        <v>4.208556734037632</v>
+        <v>4.208495502583915</v>
       </c>
       <c r="G37" t="n">
         <v>27</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1558724716310234</v>
+        <v>0.1558702037994042</v>
       </c>
       <c r="I37" t="n">
-        <v>42085.56734037632</v>
+        <v>42084.95502583915</v>
       </c>
       <c r="J37" t="n">
-        <v>1042085.567340376</v>
+        <v>1042084.955025839</v>
       </c>
       <c r="K37" t="n">
-        <v>59369.5153729961</v>
+        <v>59369.49264934134</v>
       </c>
       <c r="L37" t="n">
         <v>11.40740740740741</v>
       </c>
       <c r="M37" t="n">
-        <v>22.00225662859165</v>
+        <v>22.0022664311776</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>37.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1.155974045872327</v>
+        <v>1.155923405149649</v>
       </c>
       <c r="G38" t="n">
         <v>16</v>
       </c>
       <c r="H38" t="n">
-        <v>0.07224837786702046</v>
+        <v>0.07224521282185306</v>
       </c>
       <c r="I38" t="n">
-        <v>11559.74045872327</v>
+        <v>11559.23405149649</v>
       </c>
       <c r="J38" t="n">
-        <v>1011559.740458723</v>
+        <v>1011559.234051496</v>
       </c>
       <c r="K38" t="n">
-        <v>33752.68722282434</v>
+        <v>33752.6755145546</v>
       </c>
       <c r="L38" t="n">
         <v>10.6875</v>
       </c>
       <c r="M38" t="n">
-        <v>15.29501113708905</v>
+        <v>15.295016587735</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>37.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1.155974045872327</v>
+        <v>1.155923405149649</v>
       </c>
       <c r="G39" t="n">
         <v>16</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07224837786702046</v>
+        <v>0.07224521282185306</v>
       </c>
       <c r="I39" t="n">
-        <v>11559.74045872327</v>
+        <v>11559.23405149649</v>
       </c>
       <c r="J39" t="n">
-        <v>1011559.740458723</v>
+        <v>1011559.234051496</v>
       </c>
       <c r="K39" t="n">
-        <v>33752.68722282434</v>
+        <v>33752.6755145546</v>
       </c>
       <c r="L39" t="n">
         <v>10.6875</v>
       </c>
       <c r="M39" t="n">
-        <v>15.29501113708905</v>
+        <v>15.295016587735</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>37.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6758858331098337</v>
+        <v>-0.6759226816793206</v>
       </c>
       <c r="G40" t="n">
         <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.04224286456936461</v>
+        <v>-0.04224516760495754</v>
       </c>
       <c r="I40" t="n">
-        <v>-6758.858331098338</v>
+        <v>-6759.226816793205</v>
       </c>
       <c r="J40" t="n">
-        <v>993241.1416689017</v>
+        <v>993240.7731832068</v>
       </c>
       <c r="K40" t="n">
-        <v>33507.91842177721</v>
+        <v>33507.90884319427</v>
       </c>
       <c r="L40" t="n">
         <v>12.125</v>
       </c>
       <c r="M40" t="n">
-        <v>16.50163698653884</v>
+        <v>16.50163153589286</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>37.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6758858331098337</v>
+        <v>-0.6759226816793206</v>
       </c>
       <c r="G41" t="n">
         <v>16</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.04224286456936461</v>
+        <v>-0.04224516760495754</v>
       </c>
       <c r="I41" t="n">
-        <v>-6758.858331098338</v>
+        <v>-6759.226816793205</v>
       </c>
       <c r="J41" t="n">
-        <v>993241.1416689017</v>
+        <v>993240.7731832068</v>
       </c>
       <c r="K41" t="n">
-        <v>33507.91842177721</v>
+        <v>33507.90884319427</v>
       </c>
       <c r="L41" t="n">
         <v>12.125</v>
       </c>
       <c r="M41" t="n">
-        <v>16.50163698653884</v>
+        <v>16.50163153589286</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>37.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.810681878897885</v>
+        <v>-3.810698705084168</v>
       </c>
       <c r="G42" t="n">
         <v>16</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.2381676174311178</v>
+        <v>-0.2381686690677605</v>
       </c>
       <c r="I42" t="n">
-        <v>-38106.81878897885</v>
+        <v>-38106.98705084168</v>
       </c>
       <c r="J42" t="n">
-        <v>961893.1812110211</v>
+        <v>961893.0129491583</v>
       </c>
       <c r="K42" t="n">
-        <v>32548.91122593718</v>
+        <v>32548.90771958934</v>
       </c>
       <c r="L42" t="n">
         <v>12.4375</v>
       </c>
       <c r="M42" t="n">
-        <v>16.50163698653883</v>
+        <v>16.50163153589286</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>37.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.810681878897885</v>
+        <v>-3.810698705084168</v>
       </c>
       <c r="G43" t="n">
         <v>16</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2381676174311178</v>
+        <v>-0.2381686690677605</v>
       </c>
       <c r="I43" t="n">
-        <v>-38106.81878897885</v>
+        <v>-38106.98705084168</v>
       </c>
       <c r="J43" t="n">
-        <v>961893.1812110211</v>
+        <v>961893.0129491583</v>
       </c>
       <c r="K43" t="n">
-        <v>32548.91122593718</v>
+        <v>32548.90771958934</v>
       </c>
       <c r="L43" t="n">
         <v>12.4375</v>
       </c>
       <c r="M43" t="n">
-        <v>16.50163698653883</v>
+        <v>16.50163153589286</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.732946717138379</v>
+        <v>-6.733003681877232</v>
       </c>
       <c r="G44" t="n">
         <v>18</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3740525953965766</v>
+        <v>-0.3740557601042906</v>
       </c>
       <c r="I44" t="n">
-        <v>-67329.46717138379</v>
+        <v>-67330.03681877232</v>
       </c>
       <c r="J44" t="n">
-        <v>932670.5328286162</v>
+        <v>932669.9631812277</v>
       </c>
       <c r="K44" t="n">
-        <v>36347.00774821512</v>
+        <v>36346.99231466126</v>
       </c>
       <c r="L44" t="n">
         <v>11.11111111111111</v>
       </c>
       <c r="M44" t="n">
-        <v>18.69846659257183</v>
+        <v>18.69847154004813</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F45" t="n">
-        <v>-8.51501173380675</v>
+        <v>-8.515085124377011</v>
       </c>
       <c r="G45" t="n">
         <v>18</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4730562074337084</v>
+        <v>-0.4730602846876117</v>
       </c>
       <c r="I45" t="n">
-        <v>-85150.1173380675</v>
+        <v>-85150.8512437701</v>
       </c>
       <c r="J45" t="n">
-        <v>914849.8826619325</v>
+        <v>914849.1487562299</v>
       </c>
       <c r="K45" t="n">
-        <v>35809.47426507939</v>
+        <v>35809.45278635006</v>
       </c>
       <c r="L45" t="n">
         <v>11.27777777777778</v>
       </c>
       <c r="M45" t="n">
-        <v>19.01717373619948</v>
+        <v>19.01717866428137</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.51501173380675</v>
+        <v>-8.515085124377011</v>
       </c>
       <c r="G46" t="n">
         <v>18</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4730562074337084</v>
+        <v>-0.4730602846876117</v>
       </c>
       <c r="I46" t="n">
-        <v>-85150.1173380675</v>
+        <v>-85150.8512437701</v>
       </c>
       <c r="J46" t="n">
-        <v>914849.8826619325</v>
+        <v>914849.1487562299</v>
       </c>
       <c r="K46" t="n">
-        <v>35809.47426507939</v>
+        <v>35809.45278635006</v>
       </c>
       <c r="L46" t="n">
         <v>11.27777777777778</v>
       </c>
       <c r="M46" t="n">
-        <v>19.01717373619948</v>
+        <v>19.01717866428137</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
